--- a/Games/Booklets/Everspace 2/maps/01_Galaxy/Coordinates.xlsx
+++ b/Games/Booklets/Everspace 2/maps/01_Galaxy/Coordinates.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.bey\Documents\GitHub\homepage\Games\Booklets\Everspace 2\maps\01_Galaxy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35B03BD-C76A-4EAA-BB30-60F65A2A9EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719D15C4-889B-40B8-9498-9DDE4E658E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
+    <sheet name="Ceto" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>AETHON</t>
   </si>
@@ -87,6 +88,42 @@
   </si>
   <si>
     <t>Path-Y</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Poly 1</t>
+  </si>
+  <si>
+    <t>Poly 2</t>
+  </si>
+  <si>
+    <t>Poly 3</t>
+  </si>
+  <si>
+    <t>Poly 4</t>
+  </si>
+  <si>
+    <t>Poly 5</t>
+  </si>
+  <si>
+    <t>Poly 6</t>
+  </si>
+  <si>
+    <t>Poly 7</t>
+  </si>
+  <si>
+    <t>Poly 8</t>
+  </si>
+  <si>
+    <t>Größe</t>
+  </si>
+  <si>
+    <t>Center-X</t>
+  </si>
+  <si>
+    <t>Center-Y</t>
   </si>
 </sst>
 </file>
@@ -133,13 +170,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,13 +467,14 @@
   <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="20" width="9.140625" style="2"/>
+    <col min="1" max="1" width="20.28515625" style="2" customWidth="1"/>
+    <col min="2" max="7" width="10.140625" style="2" customWidth="1"/>
+    <col min="8" max="20" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -451,31 +495,32 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="C3" s="2">
-        <v>281</v>
+        <v>112</v>
       </c>
       <c r="D3" s="2">
         <f>B3+40</f>
-        <v>181</v>
+        <v>321</v>
       </c>
       <c r="E3" s="2">
         <f>C3+94</f>
-        <v>375</v>
+        <v>206</v>
       </c>
       <c r="F3" s="2">
         <f>B3+40</f>
-        <v>181</v>
+        <v>321</v>
       </c>
       <c r="G3" s="2">
         <f>C3+40</f>
-        <v>321</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -483,26 +528,26 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>374</v>
+        <v>698</v>
       </c>
       <c r="C4" s="2">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" ref="D4:D35" si="0">B4+40</f>
-        <v>414</v>
+        <f t="shared" ref="D4:D12" si="0">B4+40</f>
+        <v>738</v>
       </c>
       <c r="E4" s="2">
-        <f t="shared" ref="E4:E35" si="1">C4+94</f>
-        <v>369</v>
+        <f t="shared" ref="E4:E12" si="1">C4+94</f>
+        <v>194</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F12" si="2">B4+40</f>
-        <v>414</v>
+        <f t="shared" ref="F4:G12" si="2">B4+40</f>
+        <v>738</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" ref="G4:G12" si="3">C4+40</f>
-        <v>315</v>
+        <f t="shared" si="2"/>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -510,26 +555,26 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="1"/>
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="3"/>
-        <v>517</v>
+        <f t="shared" si="2"/>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -537,26 +582,26 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>222</v>
+        <v>426</v>
       </c>
       <c r="C6" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>262</v>
+        <v>466</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="1"/>
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="2"/>
-        <v>262</v>
+        <v>466</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="3"/>
-        <v>530</v>
+        <f t="shared" si="2"/>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -564,26 +609,26 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>468</v>
+        <v>861</v>
       </c>
       <c r="C7" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>508</v>
+        <v>901</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="1"/>
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="2"/>
-        <v>508</v>
+        <v>901</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" si="3"/>
-        <v>505</v>
+        <f t="shared" si="2"/>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -591,26 +636,26 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>778</v>
+        <v>1412</v>
       </c>
       <c r="C8" s="2">
-        <v>346</v>
+        <v>227</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>818</v>
+        <v>1452</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>321</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="2"/>
-        <v>818</v>
+        <v>1452</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="3"/>
-        <v>386</v>
+        <f t="shared" si="2"/>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -618,26 +663,26 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="C9" s="2">
-        <v>735</v>
+        <v>922</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="1"/>
-        <v>829</v>
+        <v>1016</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="2"/>
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="3"/>
-        <v>775</v>
+        <f t="shared" si="2"/>
+        <v>962</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -645,26 +690,26 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>496</v>
+        <v>912</v>
       </c>
       <c r="C10" s="2">
-        <v>683</v>
+        <v>826</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>536</v>
+        <v>952</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="1"/>
-        <v>777</v>
+        <v>920</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="2"/>
-        <v>536</v>
+        <v>952</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="3"/>
-        <v>723</v>
+        <f t="shared" si="2"/>
+        <v>866</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -672,26 +717,26 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>706</v>
+        <v>1286</v>
       </c>
       <c r="C11" s="2">
-        <v>643</v>
+        <v>755</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="0"/>
-        <v>746</v>
+        <v>1326</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="1"/>
-        <v>737</v>
+        <v>849</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="2"/>
-        <v>746</v>
+        <v>1326</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="3"/>
-        <v>683</v>
+        <f t="shared" si="2"/>
+        <v>795</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -699,14 +744,14 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>829</v>
+        <v>1504</v>
       </c>
       <c r="C12" s="2">
         <v>498</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
-        <v>869</v>
+        <v>1544</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="1"/>
@@ -714,15 +759,822 @@
       </c>
       <c r="F12" s="2">
         <f t="shared" si="2"/>
-        <v>869</v>
+        <v>1544</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>538</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F8B509-92C9-4A57-86A0-0F98D157BAD0}">
+  <dimension ref="A1:Y29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="1.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8" style="2" customWidth="1"/>
+    <col min="4" max="4" width="1.42578125" style="2" customWidth="1"/>
+    <col min="5" max="6" width="8" style="2" customWidth="1"/>
+    <col min="7" max="7" width="1.42578125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="1.42578125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="8" style="2" customWidth="1"/>
+    <col min="13" max="13" width="1.42578125" style="2" customWidth="1"/>
+    <col min="14" max="15" width="8" style="2" customWidth="1"/>
+    <col min="16" max="16" width="1.42578125" style="2" customWidth="1"/>
+    <col min="17" max="18" width="8" style="2" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="2" customWidth="1"/>
+    <col min="20" max="21" width="8" style="2" customWidth="1"/>
+    <col min="22" max="22" width="1.42578125" style="2" customWidth="1"/>
+    <col min="23" max="25" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2">
+        <v>600</v>
+      </c>
+      <c r="F3" s="2">
+        <v>68</v>
+      </c>
+      <c r="H3" s="2">
+        <f>E3</f>
+        <v>600</v>
+      </c>
+      <c r="I3" s="2">
+        <f>F3-(C3/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K3" s="2">
+        <f>E3+(C3/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L3" s="2">
+        <f>F3</f>
+        <v>68</v>
+      </c>
+      <c r="N3" s="2">
+        <f>E3</f>
+        <v>600</v>
+      </c>
+      <c r="O3" s="2">
+        <f>F3+(C3/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q3" s="2">
+        <f>E3-(C3/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R3" s="2">
+        <f>F3</f>
+        <v>68</v>
+      </c>
+      <c r="T3" s="2">
+        <f>E3</f>
+        <v>600</v>
+      </c>
+      <c r="U3" s="2">
+        <f>F3+C3</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3" t="str">
+        <f>H3&amp;","&amp;I3&amp;" "&amp;K3&amp;","&amp;L3&amp;" "&amp;N3&amp;","&amp;O3&amp;" "&amp;Q3&amp;","&amp;R3</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1">
+        <v>40</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="2">
+        <v>600</v>
+      </c>
+      <c r="F6" s="2">
+        <v>68</v>
+      </c>
+      <c r="H6" s="2">
+        <f>E6</f>
+        <v>600</v>
+      </c>
+      <c r="I6" s="2">
+        <f>F6-(C6/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K6" s="2">
+        <f>E6+(C6/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L6" s="2">
+        <f>F6</f>
+        <v>68</v>
+      </c>
+      <c r="N6" s="2">
+        <f>E6</f>
+        <v>600</v>
+      </c>
+      <c r="O6" s="2">
+        <f>F6+(C6/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>E6-(C6/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R6" s="2">
+        <f>F6</f>
+        <v>68</v>
+      </c>
+      <c r="T6" s="2">
+        <f>E6</f>
+        <v>600</v>
+      </c>
+      <c r="U6" s="2">
+        <f>F6+C6</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="3" t="str">
+        <f>H6&amp;","&amp;I6&amp;" "&amp;K6&amp;","&amp;L6&amp;" "&amp;N6&amp;","&amp;O6&amp;" "&amp;Q6&amp;","&amp;R6</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1">
+        <v>40</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2">
+        <v>600</v>
+      </c>
+      <c r="F9" s="2">
+        <v>68</v>
+      </c>
+      <c r="H9" s="2">
+        <f>E9</f>
+        <v>600</v>
+      </c>
+      <c r="I9" s="2">
+        <f>F9-(C9/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K9" s="2">
+        <f>E9+(C9/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L9" s="2">
+        <f>F9</f>
+        <v>68</v>
+      </c>
+      <c r="N9" s="2">
+        <f>E9</f>
+        <v>600</v>
+      </c>
+      <c r="O9" s="2">
+        <f>F9+(C9/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>E9-(C9/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R9" s="2">
+        <f>F9</f>
+        <v>68</v>
+      </c>
+      <c r="T9" s="2">
+        <f>E9</f>
+        <v>600</v>
+      </c>
+      <c r="U9" s="2">
+        <f>F9+C9</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="3" t="str">
+        <f>H9&amp;","&amp;I9&amp;" "&amp;K9&amp;","&amp;L9&amp;" "&amp;N9&amp;","&amp;O9&amp;" "&amp;Q9&amp;","&amp;R9</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2">
+        <v>600</v>
+      </c>
+      <c r="F12" s="2">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2">
+        <f>E12</f>
+        <v>600</v>
+      </c>
+      <c r="I12" s="2">
+        <f>F12-(C12/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K12" s="2">
+        <f>E12+(C12/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L12" s="2">
+        <f>F12</f>
+        <v>68</v>
+      </c>
+      <c r="N12" s="2">
+        <f>E12</f>
+        <v>600</v>
+      </c>
+      <c r="O12" s="2">
+        <f>F12+(C12/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>E12-(C12/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R12" s="2">
+        <f>F12</f>
+        <v>68</v>
+      </c>
+      <c r="T12" s="2">
+        <f>E12</f>
+        <v>600</v>
+      </c>
+      <c r="U12" s="2">
+        <f>F12+C12</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="3" t="str">
+        <f>H12&amp;","&amp;I12&amp;" "&amp;K12&amp;","&amp;L12&amp;" "&amp;N12&amp;","&amp;O12&amp;" "&amp;Q12&amp;","&amp;R12</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="2">
+        <v>600</v>
+      </c>
+      <c r="F15" s="2">
+        <v>68</v>
+      </c>
+      <c r="H15" s="2">
+        <f>E15</f>
+        <v>600</v>
+      </c>
+      <c r="I15" s="2">
+        <f>F15-(C15/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K15" s="2">
+        <f>E15+(C15/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L15" s="2">
+        <f>F15</f>
+        <v>68</v>
+      </c>
+      <c r="N15" s="2">
+        <f>E15</f>
+        <v>600</v>
+      </c>
+      <c r="O15" s="2">
+        <f>F15+(C15/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>E15-(C15/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R15" s="2">
+        <f>F15</f>
+        <v>68</v>
+      </c>
+      <c r="T15" s="2">
+        <f>E15</f>
+        <v>600</v>
+      </c>
+      <c r="U15" s="2">
+        <f>F15+C15</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="3" t="str">
+        <f>H15&amp;","&amp;I15&amp;" "&amp;K15&amp;","&amp;L15&amp;" "&amp;N15&amp;","&amp;O15&amp;" "&amp;Q15&amp;","&amp;R15</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1">
+        <v>40</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="2">
+        <v>600</v>
+      </c>
+      <c r="F18" s="2">
+        <v>68</v>
+      </c>
+      <c r="H18" s="2">
+        <f>E18</f>
+        <v>600</v>
+      </c>
+      <c r="I18" s="2">
+        <f>F18-(C18/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K18" s="2">
+        <f>E18+(C18/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L18" s="2">
+        <f>F18</f>
+        <v>68</v>
+      </c>
+      <c r="N18" s="2">
+        <f>E18</f>
+        <v>600</v>
+      </c>
+      <c r="O18" s="2">
+        <f>F18+(C18/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>E18-(C18/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R18" s="2">
+        <f>F18</f>
+        <v>68</v>
+      </c>
+      <c r="T18" s="2">
+        <f>E18</f>
+        <v>600</v>
+      </c>
+      <c r="U18" s="2">
+        <f>F18+C18</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="3" t="str">
+        <f>H18&amp;","&amp;I18&amp;" "&amp;K18&amp;","&amp;L18&amp;" "&amp;N18&amp;","&amp;O18&amp;" "&amp;Q18&amp;","&amp;R18</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1">
+        <v>40</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2">
+        <v>600</v>
+      </c>
+      <c r="F21" s="2">
+        <v>68</v>
+      </c>
+      <c r="H21" s="2">
+        <f>E21</f>
+        <v>600</v>
+      </c>
+      <c r="I21" s="2">
+        <f>F21-(C21/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K21" s="2">
+        <f>E21+(C21/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L21" s="2">
+        <f>F21</f>
+        <v>68</v>
+      </c>
+      <c r="N21" s="2">
+        <f>E21</f>
+        <v>600</v>
+      </c>
+      <c r="O21" s="2">
+        <f>F21+(C21/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q21" s="2">
+        <f>E21-(C21/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R21" s="2">
+        <f>F21</f>
+        <v>68</v>
+      </c>
+      <c r="T21" s="2">
+        <f>E21</f>
+        <v>600</v>
+      </c>
+      <c r="U21" s="2">
+        <f>F21+C21</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="3" t="str">
+        <f>H21&amp;","&amp;I21&amp;" "&amp;K21&amp;","&amp;L21&amp;" "&amp;N21&amp;","&amp;O21&amp;" "&amp;Q21&amp;","&amp;R21</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1">
+        <v>40</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="2">
+        <v>600</v>
+      </c>
+      <c r="F24" s="2">
+        <v>68</v>
+      </c>
+      <c r="H24" s="2">
+        <f>E24</f>
+        <v>600</v>
+      </c>
+      <c r="I24" s="2">
+        <f>F24-(C24/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K24" s="2">
+        <f>E24+(C24/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L24" s="2">
+        <f>F24</f>
+        <v>68</v>
+      </c>
+      <c r="N24" s="2">
+        <f>E24</f>
+        <v>600</v>
+      </c>
+      <c r="O24" s="2">
+        <f>F24+(C24/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q24" s="2">
+        <f>E24-(C24/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R24" s="2">
+        <f>F24</f>
+        <v>68</v>
+      </c>
+      <c r="T24" s="2">
+        <f>E24</f>
+        <v>600</v>
+      </c>
+      <c r="U24" s="2">
+        <f>F24+C24</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="3" t="str">
+        <f>H24&amp;","&amp;I24&amp;" "&amp;K24&amp;","&amp;L24&amp;" "&amp;N24&amp;","&amp;O24&amp;" "&amp;Q24&amp;","&amp;R24</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1">
+        <v>40</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="2">
+        <v>600</v>
+      </c>
+      <c r="F27" s="2">
+        <v>68</v>
+      </c>
+      <c r="H27" s="2">
+        <f>E27</f>
+        <v>600</v>
+      </c>
+      <c r="I27" s="2">
+        <f>F27-(C27/2)</f>
+        <v>48</v>
+      </c>
+      <c r="K27" s="2">
+        <f>E27+(C27/2)</f>
+        <v>620</v>
+      </c>
+      <c r="L27" s="2">
+        <f>F27</f>
+        <v>68</v>
+      </c>
+      <c r="N27" s="2">
+        <f>E27</f>
+        <v>600</v>
+      </c>
+      <c r="O27" s="2">
+        <f>F27+(C27/2)</f>
+        <v>88</v>
+      </c>
+      <c r="Q27" s="2">
+        <f>E27-(C27/2)</f>
+        <v>580</v>
+      </c>
+      <c r="R27" s="2">
+        <f>F27</f>
+        <v>68</v>
+      </c>
+      <c r="T27" s="2">
+        <f>E27</f>
+        <v>600</v>
+      </c>
+      <c r="U27" s="2">
+        <f>F27+C27</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="3" t="str">
+        <f>H27&amp;","&amp;I27&amp;" "&amp;K27&amp;","&amp;L27&amp;" "&amp;N27&amp;","&amp;O27&amp;" "&amp;Q27&amp;","&amp;R27</f>
+        <v>600,48 620,68 600,88 580,68</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="E22:R22"/>
+    <mergeCell ref="E25:R25"/>
+    <mergeCell ref="E28:R28"/>
+    <mergeCell ref="E4:R4"/>
+    <mergeCell ref="E7:R7"/>
+    <mergeCell ref="E10:R10"/>
+    <mergeCell ref="E13:R13"/>
+    <mergeCell ref="E16:R16"/>
+    <mergeCell ref="E19:R19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Games/Booklets/Everspace 2/maps/01_Galaxy/Coordinates.xlsx
+++ b/Games/Booklets/Everspace 2/maps/01_Galaxy/Coordinates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.bey\Documents\GitHub\homepage\Games\Booklets\Everspace 2\maps\01_Galaxy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719D15C4-889B-40B8-9498-9DDE4E658E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B40B7F-9EB7-4B75-871D-6DF36B005141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>AETHON</t>
   </si>
@@ -124,6 +124,72 @@
   </si>
   <si>
     <t>Center-Y</t>
+  </si>
+  <si>
+    <t>BERGBAU-RUINE</t>
+  </si>
+  <si>
+    <t>CETO OUTER RIM</t>
+  </si>
+  <si>
+    <t>RHODIA ORBIT</t>
+  </si>
+  <si>
+    <t>RHODIA II</t>
+  </si>
+  <si>
+    <t>UNION BRIDGE</t>
+  </si>
+  <si>
+    <t>SCHIFFSWRACK</t>
+  </si>
+  <si>
+    <t>OUTLAW GRENZLAND</t>
+  </si>
+  <si>
+    <t>ASTEROIDENFELD</t>
+  </si>
+  <si>
+    <t>VERLASSENE</t>
+  </si>
+  <si>
+    <t>STATION</t>
+  </si>
+  <si>
+    <t>OUTLAW</t>
+  </si>
+  <si>
+    <t>AUSSENPOSTEN</t>
+  </si>
+  <si>
+    <t>ZERSTÖRTE</t>
+  </si>
+  <si>
+    <t>FÖRDERSTATION</t>
+  </si>
+  <si>
+    <t>PALAEMONS WUNDE</t>
+  </si>
+  <si>
+    <t>GEISTERFLOTTE</t>
+  </si>
+  <si>
+    <t>OUTLAW-BASIS</t>
+  </si>
+  <si>
+    <t>MEER DER SIRENEN</t>
+  </si>
+  <si>
+    <t>CETO ORBIT</t>
+  </si>
+  <si>
+    <t>FÖRDERSTÄTTE</t>
+  </si>
+  <si>
+    <t>ALKIONE-STATION</t>
+  </si>
+  <si>
+    <t>VERLASSENE ANLAGE</t>
   </si>
 </sst>
 </file>
@@ -774,25 +840,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F8B509-92C9-4A57-86A0-0F98D157BAD0}">
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="1.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="1.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="1" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6" style="2" customWidth="1"/>
+    <col min="4" max="4" width="1" style="2" customWidth="1"/>
     <col min="5" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="7" width="1.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="1" style="2" customWidth="1"/>
     <col min="8" max="9" width="8" style="2" customWidth="1"/>
-    <col min="10" max="10" width="1.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="1" style="2" customWidth="1"/>
     <col min="11" max="12" width="8" style="2" customWidth="1"/>
-    <col min="13" max="13" width="1.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="1" style="2" customWidth="1"/>
     <col min="14" max="15" width="8" style="2" customWidth="1"/>
-    <col min="16" max="16" width="1.42578125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="1" style="2" customWidth="1"/>
     <col min="17" max="18" width="8" style="2" customWidth="1"/>
-    <col min="19" max="19" width="1.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="1" style="2" customWidth="1"/>
     <col min="20" max="21" width="8" style="2" customWidth="1"/>
-    <col min="22" max="22" width="1.42578125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="1" style="2" customWidth="1"/>
     <col min="23" max="25" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -842,57 +908,59 @@
     </row>
     <row r="2" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1">
         <v>40</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="2">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="F3" s="2">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="H3" s="2">
         <f>E3</f>
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="I3" s="2">
         <f>F3-(C3/2)</f>
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="K3" s="2">
         <f>E3+(C3/2)</f>
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="L3" s="2">
         <f>F3</f>
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="N3" s="2">
         <f>E3</f>
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="O3" s="2">
         <f>F3+(C3/2)</f>
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="Q3" s="2">
         <f>E3-(C3/2)</f>
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="R3" s="2">
         <f>F3</f>
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="T3" s="2">
         <f>E3</f>
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="U3" s="2">
         <f>F3+C3</f>
-        <v>108</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -900,96 +968,98 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="3" t="str">
+      <c r="E4" s="4" t="str">
         <f>H3&amp;","&amp;I3&amp;" "&amp;K3&amp;","&amp;L3&amp;" "&amp;N3&amp;","&amp;O3&amp;" "&amp;Q3&amp;","&amp;R3</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-    </row>
-    <row r="5" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+        <v>580,100 600,120 580,140 560,120</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" spans="1:21" s="2" customFormat="1" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1">
         <v>40</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="2">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="F6" s="2">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="H6" s="2">
         <f>E6</f>
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="I6" s="2">
         <f>F6-(C6/2)</f>
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="K6" s="2">
         <f>E6+(C6/2)</f>
-        <v>620</v>
+        <v>540</v>
       </c>
       <c r="L6" s="2">
         <f>F6</f>
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="N6" s="2">
         <f>E6</f>
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="O6" s="2">
         <f>F6+(C6/2)</f>
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="Q6" s="2">
         <f>E6-(C6/2)</f>
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="R6" s="2">
         <f>F6</f>
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="T6" s="2">
         <f>E6</f>
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="U6" s="2">
         <f>F6+C6</f>
-        <v>108</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -997,77 +1067,79 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="3" t="str">
+      <c r="E7" s="4" t="str">
         <f>H6&amp;","&amp;I6&amp;" "&amp;K6&amp;","&amp;L6&amp;" "&amp;N6&amp;","&amp;O6&amp;" "&amp;Q6&amp;","&amp;R6</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>520,160 540,180 520,200 500,180</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" spans="1:21" s="2" customFormat="1" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1">
         <v>40</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F9" s="2">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="H9" s="2">
         <f>E9</f>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I9" s="2">
         <f>F9-(C9/2)</f>
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="K9" s="2">
         <f>E9+(C9/2)</f>
-        <v>620</v>
+        <v>720</v>
       </c>
       <c r="L9" s="2">
         <f>F9</f>
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2">
         <f>E9</f>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O9" s="2">
         <f>F9+(C9/2)</f>
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="Q9" s="2">
         <f>E9-(C9/2)</f>
-        <v>580</v>
+        <v>680</v>
       </c>
       <c r="R9" s="2">
         <f>F9</f>
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="T9" s="2">
         <f>E9</f>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="U9" s="2">
         <f>F9+C9</f>
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1075,77 +1147,79 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="3" t="str">
+      <c r="E10" s="4" t="str">
         <f>H9&amp;","&amp;I9&amp;" "&amp;K9&amp;","&amp;L9&amp;" "&amp;N9&amp;","&amp;O9&amp;" "&amp;Q9&amp;","&amp;R9</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>700,120 720,140 700,160 680,140</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+    </row>
+    <row r="11" spans="1:21" s="2" customFormat="1" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>40</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2">
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="F12" s="2">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2">
         <f>E12</f>
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="I12" s="2">
         <f>F12-(C12/2)</f>
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="K12" s="2">
         <f>E12+(C12/2)</f>
-        <v>620</v>
+        <v>780</v>
       </c>
       <c r="L12" s="2">
         <f>F12</f>
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="N12" s="2">
         <f>E12</f>
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="O12" s="2">
         <f>F12+(C12/2)</f>
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="Q12" s="2">
         <f>E12-(C12/2)</f>
-        <v>580</v>
+        <v>740</v>
       </c>
       <c r="R12" s="2">
         <f>F12</f>
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="T12" s="2">
         <f>E12</f>
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="U12" s="2">
         <f>F12+C12</f>
-        <v>108</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1153,77 +1227,79 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="3" t="str">
+      <c r="E13" s="4" t="str">
         <f>H12&amp;","&amp;I12&amp;" "&amp;K12&amp;","&amp;L12&amp;" "&amp;N12&amp;","&amp;O12&amp;" "&amp;Q12&amp;","&amp;R12</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:21" s="2" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>760,180 780,200 760,220 740,200</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+    </row>
+    <row r="14" spans="1:21" s="2" customFormat="1" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1">
         <v>40</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="2">
-        <v>600</v>
+        <v>790</v>
       </c>
       <c r="F15" s="2">
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="H15" s="2">
         <f>E15</f>
-        <v>600</v>
+        <v>790</v>
       </c>
       <c r="I15" s="2">
         <f>F15-(C15/2)</f>
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="K15" s="2">
         <f>E15+(C15/2)</f>
-        <v>620</v>
+        <v>810</v>
       </c>
       <c r="L15" s="2">
         <f>F15</f>
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="N15" s="2">
         <f>E15</f>
-        <v>600</v>
+        <v>790</v>
       </c>
       <c r="O15" s="2">
         <f>F15+(C15/2)</f>
-        <v>88</v>
+        <v>320</v>
       </c>
       <c r="Q15" s="2">
         <f>E15-(C15/2)</f>
-        <v>580</v>
+        <v>770</v>
       </c>
       <c r="R15" s="2">
         <f>F15</f>
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="T15" s="2">
         <f>E15</f>
-        <v>600</v>
+        <v>790</v>
       </c>
       <c r="U15" s="2">
         <f>F15+C15</f>
-        <v>108</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -1231,77 +1307,78 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="3" t="str">
+      <c r="E16" s="4" t="str">
         <f>H15&amp;","&amp;I15&amp;" "&amp;K15&amp;","&amp;L15&amp;" "&amp;N15&amp;","&amp;O15&amp;" "&amp;Q15&amp;","&amp;R15</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>790,280 810,300 790,320 770,300</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+    </row>
+    <row r="17" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1">
         <v>40</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="2">
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="F18" s="2">
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="H18" s="2">
-        <f>E18</f>
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I18" s="2">
         <f>F18-(C18/2)</f>
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="K18" s="2">
         <f>E18+(C18/2)</f>
-        <v>620</v>
+        <v>980</v>
       </c>
       <c r="L18" s="2">
         <f>F18</f>
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="N18" s="2">
         <f>E18</f>
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="O18" s="2">
         <f>F18+(C18/2)</f>
-        <v>88</v>
+        <v>320</v>
       </c>
       <c r="Q18" s="2">
         <f>E18-(C18/2)</f>
-        <v>580</v>
+        <v>940</v>
       </c>
       <c r="R18" s="2">
         <f>F18</f>
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="T18" s="2">
         <f>E18</f>
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="U18" s="2">
         <f>F18+C18</f>
-        <v>108</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -1309,77 +1386,79 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="3" t="str">
+      <c r="E19" s="4" t="str">
         <f>H18&amp;","&amp;I18&amp;" "&amp;K18&amp;","&amp;L18&amp;" "&amp;N18&amp;","&amp;O18&amp;" "&amp;Q18&amp;","&amp;R18</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>300,280 980,300 960,320 940,300</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+    </row>
+    <row r="20" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1">
         <v>40</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="2">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="F21" s="2">
-        <v>68</v>
+        <v>382</v>
       </c>
       <c r="H21" s="2">
         <f>E21</f>
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="I21" s="2">
         <f>F21-(C21/2)</f>
-        <v>48</v>
+        <v>362</v>
       </c>
       <c r="K21" s="2">
         <f>E21+(C21/2)</f>
-        <v>620</v>
+        <v>690</v>
       </c>
       <c r="L21" s="2">
         <f>F21</f>
-        <v>68</v>
+        <v>382</v>
       </c>
       <c r="N21" s="2">
         <f>E21</f>
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="O21" s="2">
         <f>F21+(C21/2)</f>
-        <v>88</v>
+        <v>402</v>
       </c>
       <c r="Q21" s="2">
         <f>E21-(C21/2)</f>
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="R21" s="2">
         <f>F21</f>
-        <v>68</v>
+        <v>382</v>
       </c>
       <c r="T21" s="2">
         <f>E21</f>
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="U21" s="2">
         <f>F21+C21</f>
-        <v>108</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -1387,77 +1466,79 @@
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="3" t="str">
+      <c r="E22" s="4" t="str">
         <f>H21&amp;","&amp;I21&amp;" "&amp;K21&amp;","&amp;L21&amp;" "&amp;N21&amp;","&amp;O21&amp;" "&amp;Q21&amp;","&amp;R21</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>670,362 690,382 670,402 650,382</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+    </row>
+    <row r="23" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
         <v>40</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="2">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="F24" s="2">
-        <v>68</v>
+        <v>436</v>
       </c>
       <c r="H24" s="2">
         <f>E24</f>
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="I24" s="2">
         <f>F24-(C24/2)</f>
-        <v>48</v>
+        <v>416</v>
       </c>
       <c r="K24" s="2">
         <f>E24+(C24/2)</f>
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="L24" s="2">
         <f>F24</f>
-        <v>68</v>
+        <v>436</v>
       </c>
       <c r="N24" s="2">
         <f>E24</f>
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="O24" s="2">
         <f>F24+(C24/2)</f>
-        <v>88</v>
+        <v>456</v>
       </c>
       <c r="Q24" s="2">
         <f>E24-(C24/2)</f>
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="R24" s="2">
         <f>F24</f>
-        <v>68</v>
+        <v>436</v>
       </c>
       <c r="T24" s="2">
         <f>E24</f>
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="U24" s="2">
         <f>F24+C24</f>
-        <v>108</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -1465,105 +1546,1365 @@
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="3" t="str">
+      <c r="E25" s="4" t="str">
         <f>H24&amp;","&amp;I24&amp;" "&amp;K24&amp;","&amp;L24&amp;" "&amp;N24&amp;","&amp;O24&amp;" "&amp;Q24&amp;","&amp;R24</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>588,416 608,436 588,456 568,436</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+    </row>
+    <row r="26" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1">
         <v>40</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="2">
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="F27" s="2">
-        <v>68</v>
+        <v>470</v>
       </c>
       <c r="H27" s="2">
         <f>E27</f>
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="I27" s="2">
         <f>F27-(C27/2)</f>
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="K27" s="2">
         <f>E27+(C27/2)</f>
-        <v>620</v>
+        <v>410</v>
       </c>
       <c r="L27" s="2">
         <f>F27</f>
-        <v>68</v>
+        <v>470</v>
       </c>
       <c r="N27" s="2">
         <f>E27</f>
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="O27" s="2">
         <f>F27+(C27/2)</f>
-        <v>88</v>
+        <v>490</v>
       </c>
       <c r="Q27" s="2">
         <f>E27-(C27/2)</f>
-        <v>580</v>
+        <v>370</v>
       </c>
       <c r="R27" s="2">
         <f>F27</f>
-        <v>68</v>
+        <v>470</v>
       </c>
       <c r="T27" s="2">
         <f>E27</f>
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="U27" s="2">
         <f>F27+C27</f>
-        <v>108</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="3" t="str">
+      <c r="E28" s="4" t="str">
         <f>H27&amp;","&amp;I27&amp;" "&amp;K27&amp;","&amp;L27&amp;" "&amp;N27&amp;","&amp;O27&amp;" "&amp;Q27&amp;","&amp;R27</f>
-        <v>600,48 620,68 600,88 580,68</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="1:21" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>390,450 410,470 390,490 370,470</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+    </row>
+    <row r="29" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1">
+        <v>40</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="2">
+        <v>288</v>
+      </c>
+      <c r="F30" s="2">
+        <v>268</v>
+      </c>
+      <c r="H30" s="2">
+        <f>E30</f>
+        <v>288</v>
+      </c>
+      <c r="I30" s="2">
+        <f>F30-(C30/2)</f>
+        <v>248</v>
+      </c>
+      <c r="K30" s="2">
+        <f>E30+(C30/2)</f>
+        <v>308</v>
+      </c>
+      <c r="L30" s="2">
+        <f>F30</f>
+        <v>268</v>
+      </c>
+      <c r="N30" s="2">
+        <f>E30</f>
+        <v>288</v>
+      </c>
+      <c r="O30" s="2">
+        <f>F30+(C30/2)</f>
+        <v>288</v>
+      </c>
+      <c r="Q30" s="2">
+        <f>E30-(C30/2)</f>
+        <v>268</v>
+      </c>
+      <c r="R30" s="2">
+        <f>F30</f>
+        <v>268</v>
+      </c>
+      <c r="T30" s="2">
+        <f>E30</f>
+        <v>288</v>
+      </c>
+      <c r="U30" s="2">
+        <f>F30+C30</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="4" t="str">
+        <f>H30&amp;","&amp;I30&amp;" "&amp;K30&amp;","&amp;L30&amp;" "&amp;N30&amp;","&amp;O30&amp;" "&amp;Q30&amp;","&amp;R30</f>
+        <v>288,248 308,268 288,288 268,268</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+    </row>
+    <row r="32" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1">
+        <v>40</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="2">
+        <v>100</v>
+      </c>
+      <c r="F33" s="2">
+        <v>470</v>
+      </c>
+      <c r="H33" s="2">
+        <f>E33</f>
+        <v>100</v>
+      </c>
+      <c r="I33" s="2">
+        <f>F33-(C33/2)</f>
+        <v>450</v>
+      </c>
+      <c r="K33" s="2">
+        <f>E33+(C33/2)</f>
+        <v>120</v>
+      </c>
+      <c r="L33" s="2">
+        <f>F33</f>
+        <v>470</v>
+      </c>
+      <c r="N33" s="2">
+        <f>E33</f>
+        <v>100</v>
+      </c>
+      <c r="O33" s="2">
+        <f>F33+(C33/2)</f>
+        <v>490</v>
+      </c>
+      <c r="Q33" s="2">
+        <f>E33-(C33/2)</f>
+        <v>80</v>
+      </c>
+      <c r="R33" s="2">
+        <f>F33</f>
+        <v>470</v>
+      </c>
+      <c r="T33" s="2">
+        <f>E33</f>
+        <v>100</v>
+      </c>
+      <c r="U33" s="2">
+        <f>F33+C33</f>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="4" t="str">
+        <f>H33&amp;","&amp;I33&amp;" "&amp;K33&amp;","&amp;L33&amp;" "&amp;N33&amp;","&amp;O33&amp;" "&amp;Q33&amp;","&amp;R33</f>
+        <v>100,450 120,470 100,490 80,470</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+    </row>
+    <row r="35" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1">
+        <v>40</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="2">
+        <v>140</v>
+      </c>
+      <c r="F36" s="2">
+        <v>540</v>
+      </c>
+      <c r="H36" s="2">
+        <f>E36</f>
+        <v>140</v>
+      </c>
+      <c r="I36" s="2">
+        <f>F36-(C36/2)</f>
+        <v>520</v>
+      </c>
+      <c r="K36" s="2">
+        <f>E36+(C36/2)</f>
+        <v>160</v>
+      </c>
+      <c r="L36" s="2">
+        <f>F36</f>
+        <v>540</v>
+      </c>
+      <c r="N36" s="2">
+        <f>E36</f>
+        <v>140</v>
+      </c>
+      <c r="O36" s="2">
+        <f>F36+(C36/2)</f>
+        <v>560</v>
+      </c>
+      <c r="Q36" s="2">
+        <f>E36-(C36/2)</f>
+        <v>120</v>
+      </c>
+      <c r="R36" s="2">
+        <f>F36</f>
+        <v>540</v>
+      </c>
+      <c r="T36" s="2">
+        <f>E36</f>
+        <v>140</v>
+      </c>
+      <c r="U36" s="2">
+        <f>F36+C36</f>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="4" t="str">
+        <f>H36&amp;","&amp;I36&amp;" "&amp;K36&amp;","&amp;L36&amp;" "&amp;N36&amp;","&amp;O36&amp;" "&amp;Q36&amp;","&amp;R36</f>
+        <v>140,520 160,540 140,560 120,540</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+    </row>
+    <row r="38" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
+        <v>40</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2">
+        <v>180</v>
+      </c>
+      <c r="F39" s="2">
+        <v>570</v>
+      </c>
+      <c r="H39" s="2">
+        <f>E39</f>
+        <v>180</v>
+      </c>
+      <c r="I39" s="2">
+        <f>F39-(C39/2)</f>
+        <v>550</v>
+      </c>
+      <c r="K39" s="2">
+        <f>E39+(C39/2)</f>
+        <v>200</v>
+      </c>
+      <c r="L39" s="2">
+        <f>F39</f>
+        <v>570</v>
+      </c>
+      <c r="N39" s="2">
+        <f>E39</f>
+        <v>180</v>
+      </c>
+      <c r="O39" s="2">
+        <f>F39+(C39/2)</f>
+        <v>590</v>
+      </c>
+      <c r="Q39" s="2">
+        <f>E39-(C39/2)</f>
+        <v>160</v>
+      </c>
+      <c r="R39" s="2">
+        <f>F39</f>
+        <v>570</v>
+      </c>
+      <c r="T39" s="2">
+        <f>E39</f>
+        <v>180</v>
+      </c>
+      <c r="U39" s="2">
+        <f>F39+C39</f>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="4" t="str">
+        <f>H39&amp;","&amp;I39&amp;" "&amp;K39&amp;","&amp;L39&amp;" "&amp;N39&amp;","&amp;O39&amp;" "&amp;Q39&amp;","&amp;R39</f>
+        <v>180,550 200,570 180,590 160,570</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+    </row>
+    <row r="41" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1">
+        <v>40</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="2">
+        <v>348</v>
+      </c>
+      <c r="F43" s="2">
+        <v>534</v>
+      </c>
+      <c r="H43" s="2">
+        <f>E43</f>
+        <v>348</v>
+      </c>
+      <c r="I43" s="2">
+        <f>F43-(C43/2)</f>
+        <v>514</v>
+      </c>
+      <c r="K43" s="2">
+        <f>E43+(C43/2)</f>
+        <v>368</v>
+      </c>
+      <c r="L43" s="2">
+        <f>F43</f>
+        <v>534</v>
+      </c>
+      <c r="N43" s="2">
+        <f>E43</f>
+        <v>348</v>
+      </c>
+      <c r="O43" s="2">
+        <f>F43+(C43/2)</f>
+        <v>554</v>
+      </c>
+      <c r="Q43" s="2">
+        <f>E43-(C43/2)</f>
+        <v>328</v>
+      </c>
+      <c r="R43" s="2">
+        <f>F43</f>
+        <v>534</v>
+      </c>
+      <c r="T43" s="2">
+        <f>E43</f>
+        <v>348</v>
+      </c>
+      <c r="U43" s="2">
+        <f>F43+C43</f>
+        <v>574</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="4" t="str">
+        <f>H43&amp;","&amp;I43&amp;" "&amp;K43&amp;","&amp;L43&amp;" "&amp;N43&amp;","&amp;O43&amp;" "&amp;Q43&amp;","&amp;R43</f>
+        <v>348,514 368,534 348,554 328,534</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+    </row>
+    <row r="45" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1">
+        <v>40</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="2">
+        <v>406</v>
+      </c>
+      <c r="F46" s="2">
+        <v>558</v>
+      </c>
+      <c r="H46" s="2">
+        <f>E46</f>
+        <v>406</v>
+      </c>
+      <c r="I46" s="2">
+        <f>F46-(C46/2)</f>
+        <v>538</v>
+      </c>
+      <c r="K46" s="2">
+        <f>E46+(C46/2)</f>
+        <v>426</v>
+      </c>
+      <c r="L46" s="2">
+        <f>F46</f>
+        <v>558</v>
+      </c>
+      <c r="N46" s="2">
+        <f>E46</f>
+        <v>406</v>
+      </c>
+      <c r="O46" s="2">
+        <f>F46+(C46/2)</f>
+        <v>578</v>
+      </c>
+      <c r="Q46" s="2">
+        <f>E46-(C46/2)</f>
+        <v>386</v>
+      </c>
+      <c r="R46" s="2">
+        <f>F46</f>
+        <v>558</v>
+      </c>
+      <c r="T46" s="2">
+        <f>E46</f>
+        <v>406</v>
+      </c>
+      <c r="U46" s="2">
+        <f>F46+C46</f>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="4" t="str">
+        <f>H46&amp;","&amp;I46&amp;" "&amp;K46&amp;","&amp;L46&amp;" "&amp;N46&amp;","&amp;O46&amp;" "&amp;Q46&amp;","&amp;R46</f>
+        <v>406,538 426,558 406,578 386,558</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+    </row>
+    <row r="48" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1">
+        <v>40</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="2">
+        <v>550</v>
+      </c>
+      <c r="F49" s="2">
+        <v>564</v>
+      </c>
+      <c r="H49" s="2">
+        <f>E49</f>
+        <v>550</v>
+      </c>
+      <c r="I49" s="2">
+        <f>F49-(C49/2)</f>
+        <v>544</v>
+      </c>
+      <c r="K49" s="2">
+        <f>E49+(C49/2)</f>
+        <v>570</v>
+      </c>
+      <c r="L49" s="2">
+        <f>F49</f>
+        <v>564</v>
+      </c>
+      <c r="N49" s="2">
+        <f>E49</f>
+        <v>550</v>
+      </c>
+      <c r="O49" s="2">
+        <f>F49+(C49/2)</f>
+        <v>584</v>
+      </c>
+      <c r="Q49" s="2">
+        <f>E49-(C49/2)</f>
+        <v>530</v>
+      </c>
+      <c r="R49" s="2">
+        <f>F49</f>
+        <v>564</v>
+      </c>
+      <c r="T49" s="2">
+        <f>E49</f>
+        <v>550</v>
+      </c>
+      <c r="U49" s="2">
+        <f>F49+C49</f>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="4" t="str">
+        <f>H49&amp;","&amp;I49&amp;" "&amp;K49&amp;","&amp;L49&amp;" "&amp;N49&amp;","&amp;O49&amp;" "&amp;Q49&amp;","&amp;R49</f>
+        <v>550,544 570,564 550,584 530,564</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+    </row>
+    <row r="51" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1">
+        <v>40</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="2">
+        <v>640</v>
+      </c>
+      <c r="F52" s="2">
+        <v>530</v>
+      </c>
+      <c r="H52" s="2">
+        <f>E52</f>
+        <v>640</v>
+      </c>
+      <c r="I52" s="2">
+        <f>F52-(C52/2)</f>
+        <v>510</v>
+      </c>
+      <c r="K52" s="2">
+        <f>E52+(C52/2)</f>
+        <v>660</v>
+      </c>
+      <c r="L52" s="2">
+        <f>F52</f>
+        <v>530</v>
+      </c>
+      <c r="N52" s="2">
+        <f>E52</f>
+        <v>640</v>
+      </c>
+      <c r="O52" s="2">
+        <f>F52+(C52/2)</f>
+        <v>550</v>
+      </c>
+      <c r="Q52" s="2">
+        <f>E52-(C52/2)</f>
+        <v>620</v>
+      </c>
+      <c r="R52" s="2">
+        <f>F52</f>
+        <v>530</v>
+      </c>
+      <c r="T52" s="2">
+        <f>E52</f>
+        <v>640</v>
+      </c>
+      <c r="U52" s="2">
+        <f>F52+C52</f>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="4" t="str">
+        <f>H52&amp;","&amp;I52&amp;" "&amp;K52&amp;","&amp;L52&amp;" "&amp;N52&amp;","&amp;O52&amp;" "&amp;Q52&amp;","&amp;R52</f>
+        <v>640,510 660,530 640,550 620,530</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+    </row>
+    <row r="54" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1">
+        <v>40</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="2">
+        <v>736</v>
+      </c>
+      <c r="F55" s="2">
+        <v>460</v>
+      </c>
+      <c r="H55" s="2">
+        <f>E55</f>
+        <v>736</v>
+      </c>
+      <c r="I55" s="2">
+        <f>F55-(C55/2)</f>
+        <v>440</v>
+      </c>
+      <c r="K55" s="2">
+        <f>E55+(C55/2)</f>
+        <v>756</v>
+      </c>
+      <c r="L55" s="2">
+        <f>F55</f>
+        <v>460</v>
+      </c>
+      <c r="N55" s="2">
+        <f>E55</f>
+        <v>736</v>
+      </c>
+      <c r="O55" s="2">
+        <f>F55+(C55/2)</f>
+        <v>480</v>
+      </c>
+      <c r="Q55" s="2">
+        <f>E55-(C55/2)</f>
+        <v>716</v>
+      </c>
+      <c r="R55" s="2">
+        <f>F55</f>
+        <v>460</v>
+      </c>
+      <c r="T55" s="2">
+        <f>E55</f>
+        <v>736</v>
+      </c>
+      <c r="U55" s="2">
+        <f>F55+C55</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="4" t="str">
+        <f>H55&amp;","&amp;I55&amp;" "&amp;K55&amp;","&amp;L55&amp;" "&amp;N55&amp;","&amp;O55&amp;" "&amp;Q55&amp;","&amp;R55</f>
+        <v>736,440 756,460 736,480 716,460</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+    </row>
+    <row r="57" spans="1:21" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1">
+        <v>40</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="2">
+        <v>884</v>
+      </c>
+      <c r="F58" s="2">
+        <v>462</v>
+      </c>
+      <c r="H58" s="2">
+        <f>E58</f>
+        <v>884</v>
+      </c>
+      <c r="I58" s="2">
+        <f>F58-(C58/2)</f>
+        <v>442</v>
+      </c>
+      <c r="K58" s="2">
+        <f>E58+(C58/2)</f>
+        <v>904</v>
+      </c>
+      <c r="L58" s="2">
+        <f>F58</f>
+        <v>462</v>
+      </c>
+      <c r="N58" s="2">
+        <f>E58</f>
+        <v>884</v>
+      </c>
+      <c r="O58" s="2">
+        <f>F58+(C58/2)</f>
+        <v>482</v>
+      </c>
+      <c r="Q58" s="2">
+        <f>E58-(C58/2)</f>
+        <v>864</v>
+      </c>
+      <c r="R58" s="2">
+        <f>F58</f>
+        <v>462</v>
+      </c>
+      <c r="T58" s="2">
+        <f>E58</f>
+        <v>884</v>
+      </c>
+      <c r="U58" s="2">
+        <f>F58+C58</f>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="4" t="str">
+        <f>H58&amp;","&amp;I58&amp;" "&amp;K58&amp;","&amp;L58&amp;" "&amp;N58&amp;","&amp;O58&amp;" "&amp;Q58&amp;","&amp;R58</f>
+        <v>884,442 904,462 884,482 864,462</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1">
+        <v>40</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="2">
+        <v>1012</v>
+      </c>
+      <c r="F61" s="2">
+        <v>600</v>
+      </c>
+      <c r="H61" s="2">
+        <f>E61</f>
+        <v>1012</v>
+      </c>
+      <c r="I61" s="2">
+        <f>F61-(C61/2)</f>
+        <v>580</v>
+      </c>
+      <c r="K61" s="2">
+        <f>E61+(C61/2)</f>
+        <v>1032</v>
+      </c>
+      <c r="L61" s="2">
+        <f>F61</f>
+        <v>600</v>
+      </c>
+      <c r="N61" s="2">
+        <f>E61</f>
+        <v>1012</v>
+      </c>
+      <c r="O61" s="2">
+        <f>F61+(C61/2)</f>
+        <v>620</v>
+      </c>
+      <c r="Q61" s="2">
+        <f>E61-(C61/2)</f>
+        <v>992</v>
+      </c>
+      <c r="R61" s="2">
+        <f>F61</f>
+        <v>600</v>
+      </c>
+      <c r="T61" s="2">
+        <f>E61</f>
+        <v>1012</v>
+      </c>
+      <c r="U61" s="2">
+        <f>F61+C61</f>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="4" t="str">
+        <f>H61&amp;","&amp;I61&amp;" "&amp;K61&amp;","&amp;L61&amp;" "&amp;N61&amp;","&amp;O61&amp;" "&amp;Q61&amp;","&amp;R61</f>
+        <v>1012,580 1032,600 1012,620 992,600</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1">
+        <v>40</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="H64" s="2">
+        <f>E64</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="2">
+        <f>F64-(C64/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="K64" s="2">
+        <f>E64+(C64/2)</f>
+        <v>20</v>
+      </c>
+      <c r="L64" s="2">
+        <f>F64</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="2">
+        <f>E64</f>
+        <v>0</v>
+      </c>
+      <c r="O64" s="2">
+        <f>F64+(C64/2)</f>
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2">
+        <f>E64-(C64/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="R64" s="2">
+        <f>F64</f>
+        <v>0</v>
+      </c>
+      <c r="T64" s="2">
+        <f>E64</f>
+        <v>0</v>
+      </c>
+      <c r="U64" s="2">
+        <f>F64+C64</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="4" t="str">
+        <f>H64&amp;","&amp;I64&amp;" "&amp;K64&amp;","&amp;L64&amp;" "&amp;N64&amp;","&amp;O64&amp;" "&amp;Q64&amp;","&amp;R64</f>
+        <v>0,-20 20,0 0,20 -20,0</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1">
+        <v>40</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="H67" s="2">
+        <f>E67</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="2">
+        <f>F67-(C67/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="K67" s="2">
+        <f>E67+(C67/2)</f>
+        <v>20</v>
+      </c>
+      <c r="L67" s="2">
+        <f>F67</f>
+        <v>0</v>
+      </c>
+      <c r="N67" s="2">
+        <f>E67</f>
+        <v>0</v>
+      </c>
+      <c r="O67" s="2">
+        <f>F67+(C67/2)</f>
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2">
+        <f>E67-(C67/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="R67" s="2">
+        <f>F67</f>
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
+        <f>E67</f>
+        <v>0</v>
+      </c>
+      <c r="U67" s="2">
+        <f>F67+C67</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="4" t="str">
+        <f>H67&amp;","&amp;I67&amp;" "&amp;K67&amp;","&amp;L67&amp;" "&amp;N67&amp;","&amp;O67&amp;" "&amp;Q67&amp;","&amp;R67</f>
+        <v>0,-20 20,0 0,20 -20,0</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1">
+        <v>40</v>
+      </c>
+      <c r="D70" s="1"/>
+      <c r="H70" s="2">
+        <f>E70</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="2">
+        <f>F70-(C70/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="K70" s="2">
+        <f>E70+(C70/2)</f>
+        <v>20</v>
+      </c>
+      <c r="L70" s="2">
+        <f>F70</f>
+        <v>0</v>
+      </c>
+      <c r="N70" s="2">
+        <f>E70</f>
+        <v>0</v>
+      </c>
+      <c r="O70" s="2">
+        <f>F70+(C70/2)</f>
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2">
+        <f>E70-(C70/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="R70" s="2">
+        <f>F70</f>
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
+        <f>E70</f>
+        <v>0</v>
+      </c>
+      <c r="U70" s="2">
+        <f>F70+C70</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="4" t="str">
+        <f>H70&amp;","&amp;I70&amp;" "&amp;K70&amp;","&amp;L70&amp;" "&amp;N70&amp;","&amp;O70&amp;" "&amp;Q70&amp;","&amp;R70</f>
+        <v>0,-20 20,0 0,20 -20,0</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1">
+        <v>40</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="H73" s="2">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="2">
+        <f>F73-(C73/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="K73" s="2">
+        <f>E73+(C73/2)</f>
+        <v>20</v>
+      </c>
+      <c r="L73" s="2">
+        <f>F73</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="2">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <f>F73+(C73/2)</f>
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2">
+        <f>E73-(C73/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="R73" s="2">
+        <f>F73</f>
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="U73" s="2">
+        <f>F73+C73</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="4" t="str">
+        <f>H73&amp;","&amp;I73&amp;" "&amp;K73&amp;","&amp;L73&amp;" "&amp;N73&amp;","&amp;O73&amp;" "&amp;Q73&amp;","&amp;R73</f>
+        <v>0,-20 20,0 0,20 -20,0</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1">
+        <v>40</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="H76" s="2">
+        <f>E76</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="2">
+        <f>F76-(C76/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="K76" s="2">
+        <f>E76+(C76/2)</f>
+        <v>20</v>
+      </c>
+      <c r="L76" s="2">
+        <f>F76</f>
+        <v>0</v>
+      </c>
+      <c r="N76" s="2">
+        <f>E76</f>
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <f>F76+(C76/2)</f>
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2">
+        <f>E76-(C76/2)</f>
+        <v>-20</v>
+      </c>
+      <c r="R76" s="2">
+        <f>F76</f>
+        <v>0</v>
+      </c>
+      <c r="T76" s="2">
+        <f>E76</f>
+        <v>0</v>
+      </c>
+      <c r="U76" s="2">
+        <f>F76+C76</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="4" t="str">
+        <f>H76&amp;","&amp;I76&amp;" "&amp;K76&amp;","&amp;L76&amp;" "&amp;N76&amp;","&amp;O76&amp;" "&amp;Q76&amp;","&amp;R76</f>
+        <v>0,-20 20,0 0,20 -20,0</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="25">
+    <mergeCell ref="E77:R77"/>
+    <mergeCell ref="E62:R62"/>
+    <mergeCell ref="E65:R65"/>
+    <mergeCell ref="E68:R68"/>
+    <mergeCell ref="E71:R71"/>
+    <mergeCell ref="E74:R74"/>
+    <mergeCell ref="E47:R47"/>
+    <mergeCell ref="E50:R50"/>
+    <mergeCell ref="E53:R53"/>
+    <mergeCell ref="E56:R56"/>
+    <mergeCell ref="E59:R59"/>
+    <mergeCell ref="E31:R31"/>
+    <mergeCell ref="E34:R34"/>
+    <mergeCell ref="E37:R37"/>
+    <mergeCell ref="E40:R40"/>
+    <mergeCell ref="E44:R44"/>
     <mergeCell ref="E22:R22"/>
     <mergeCell ref="E25:R25"/>
     <mergeCell ref="E28:R28"/>
